--- a/astro-site/public/dl/food-truck-checklist-templates/06-food-truck-duties-by-role.xlsx
+++ b/astro-site/public/dl/food-truck-checklist-templates/06-food-truck-duties-by-role.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Any time</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
